--- a/public/exports/26696348.xlsx
+++ b/public/exports/26696348.xlsx
@@ -331,7 +331,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">288460</t>
+          <t xml:space="preserve">288308, 288309</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -340,7 +340,7 @@
         </is>
       </c>
       <c r="F7">
-        <v>820</v>
+        <v>2282</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,7 +381,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">501202, 501203, 5148340</t>
+          <t xml:space="preserve">288458, 288459</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -390,7 +390,7 @@
         </is>
       </c>
       <c r="F8">
-        <v>996</v>
+        <v>1231</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146394</t>
+          <t xml:space="preserve">288460</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>465</v>
+        <v>820</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146394</t>
+          <t xml:space="preserve">501202, 501203, 5148340</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F10">
-        <v>575</v>
+        <v>996</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -536,11 +536,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F11">
-        <v>1069</v>
+        <v>465</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146695</t>
+          <t xml:space="preserve">5146394</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F12">
-        <v>988</v>
+        <v>575</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146695</t>
+          <t xml:space="preserve">5146394</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F13">
-        <v>375</v>
+        <v>1069</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146874</t>
+          <t xml:space="preserve">5146695</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F14">
-        <v>495</v>
+        <v>988</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146874</t>
+          <t xml:space="preserve">5146695</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F15">
-        <v>1206</v>
+        <v>375</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -786,11 +786,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F16">
-        <v>613</v>
+        <v>495</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -836,11 +836,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F17">
-        <v>2030</v>
+        <v>1206</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F18">
-        <v>944</v>
+        <v>613</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5150673</t>
+          <t xml:space="preserve">5146874</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F19">
-        <v>559</v>
+        <v>2030</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5152174</t>
+          <t xml:space="preserve">5146874</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F20">
-        <v>512</v>
+        <v>944</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5152174</t>
+          <t xml:space="preserve">5150673</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F21">
-        <v>778</v>
+        <v>559</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5152476</t>
+          <t xml:space="preserve">5152174</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F22">
-        <v>736</v>
+        <v>512</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5152476</t>
+          <t xml:space="preserve">5152174</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F23">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5154831</t>
+          <t xml:space="preserve">5152476</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="F24">
-        <v>422</v>
+        <v>736</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5158110</t>
+          <t xml:space="preserve">5152476</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F25">
-        <v>412</v>
+        <v>778</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5158331</t>
+          <t xml:space="preserve">5154831</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F26">
-        <v>272</v>
+        <v>422</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5160838</t>
+          <t xml:space="preserve">5158110</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="F27">
-        <v>883</v>
+        <v>412</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5160838</t>
+          <t xml:space="preserve">5158331</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F28">
-        <v>1892</v>
+        <v>272</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5161330</t>
+          <t xml:space="preserve">5160838</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="F29">
-        <v>269</v>
+        <v>883</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5162197</t>
+          <t xml:space="preserve">5160838</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F30">
-        <v>411</v>
+        <v>1892</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5162695</t>
+          <t xml:space="preserve">5161330</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F31">
-        <v>1555</v>
+        <v>269</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5164440</t>
+          <t xml:space="preserve">5162197</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F32">
-        <v>2054</v>
+        <v>411</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5164440</t>
+          <t xml:space="preserve">5397138</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F33">
-        <v>367</v>
+        <v>1289</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1686,11 +1686,11 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F34">
-        <v>1289</v>
+        <v>865</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1736,11 +1736,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F35">
-        <v>865</v>
+        <v>840</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1786,11 +1786,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F36">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397138</t>
+          <t xml:space="preserve">5401340</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F37">
-        <v>835</v>
+        <v>1508</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,16 +1881,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397680</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F38">
-        <v>772</v>
+        <v>595</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397680</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F39">
-        <v>347</v>
+        <v>474</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397680</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F40">
-        <v>1306</v>
+        <v>904</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397680</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F41">
-        <v>820</v>
+        <v>920</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5399685</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F42">
-        <v>256</v>
+        <v>827</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400670</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F43">
-        <v>276</v>
+        <v>490</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5401340</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F44">
-        <v>1508</v>
+        <v>667</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2236,11 +2236,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F45">
-        <v>595</v>
+        <v>522</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5403668</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F46">
-        <v>474</v>
+        <v>847</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5404014</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F47">
-        <v>904</v>
+        <v>1827</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,16 +2381,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5404454</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F48">
-        <v>920</v>
+        <v>314</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5404454</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F49">
-        <v>827</v>
+        <v>501</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2481,16 +2481,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5404454</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F50">
-        <v>490</v>
+        <v>633</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5404454</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F51">
-        <v>667</v>
+        <v>732</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5404454</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="F52">
-        <v>522</v>
+        <v>1652</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403668</t>
+          <t xml:space="preserve">5407641</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F53">
-        <v>847</v>
+        <v>300</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404014</t>
+          <t xml:space="preserve">5408397</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="F54">
-        <v>1827</v>
+        <v>646</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404454</t>
+          <t xml:space="preserve">5408398</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="F55">
-        <v>314</v>
+        <v>353</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2781,16 +2781,16 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404454</t>
+          <t xml:space="preserve">5409685</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
-        <v>501</v>
+        <v>3052</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404454</t>
+          <t xml:space="preserve">5409685</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F57">
-        <v>633</v>
+        <v>897</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2881,16 +2881,16 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404454</t>
+          <t xml:space="preserve">5409685</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F58">
-        <v>732</v>
+        <v>290</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,16 +2931,16 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404454</t>
+          <t xml:space="preserve">5409689</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F59">
-        <v>1652</v>
+        <v>668</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405178</t>
+          <t xml:space="preserve">5410241</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="F60">
-        <v>253</v>
+        <v>519</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3031,16 +3031,16 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407641</t>
+          <t xml:space="preserve">5410241</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F61">
-        <v>300</v>
+        <v>570</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3081,16 +3081,16 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5408397</t>
+          <t xml:space="preserve">5410241</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F62">
-        <v>646</v>
+        <v>1447</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3131,16 +3131,16 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5408398</t>
+          <t xml:space="preserve">5410241</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F63">
-        <v>353</v>
+        <v>1584</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3181,16 +3181,16 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409685</t>
+          <t xml:space="preserve">5410241</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F64">
-        <v>3052</v>
+        <v>384</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409685</t>
+          <t xml:space="preserve">5412912</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F65">
-        <v>897</v>
+        <v>420</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3281,16 +3281,16 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409685</t>
+          <t xml:space="preserve">725177, 5165787</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F66">
-        <v>290</v>
+        <v>979</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3331,16 +3331,16 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409689</t>
+          <t xml:space="preserve">725209, 5400294</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F67">
-        <v>668</v>
+        <v>525</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3381,16 +3381,16 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410241</t>
+          <t xml:space="preserve">725214, 5167017</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F68">
-        <v>519</v>
+        <v>1751</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3431,16 +3431,16 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410241</t>
+          <t xml:space="preserve">725254, 5401425</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F69">
-        <v>570</v>
+        <v>499</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3481,16 +3481,16 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410241</t>
+          <t xml:space="preserve">725364, 5159745</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F70">
-        <v>1447</v>
+        <v>262</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3531,16 +3531,16 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410241</t>
+          <t xml:space="preserve">725513, 5408522</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F71">
-        <v>1584</v>
+        <v>421</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3581,16 +3581,16 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410241</t>
+          <t xml:space="preserve">725541, 5409688</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F72">
-        <v>384</v>
+        <v>532</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3631,16 +3631,16 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5412912</t>
+          <t xml:space="preserve">725542, 5409686</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F73">
-        <v>420</v>
+        <v>363</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3681,16 +3681,16 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">725159, 5166867</t>
+          <t xml:space="preserve">725544, 5409689</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F74">
-        <v>575</v>
+        <v>1526</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3731,16 +3731,16 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">725177, 5165787</t>
+          <t xml:space="preserve">725553, 5146977</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F75">
-        <v>979</v>
+        <v>998</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">725180, 5398549</t>
+          <t xml:space="preserve">725622, 5397851</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="F76">
-        <v>1129</v>
+        <v>4070</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3831,16 +3831,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">725184, 5399685</t>
+          <t xml:space="preserve">725657, 5153397</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F77">
-        <v>418</v>
+        <v>378</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3881,16 +3881,16 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">725184, 5399685</t>
+          <t xml:space="preserve">725741, 5397656</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F78">
-        <v>691</v>
+        <v>1771</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3931,16 +3931,16 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">725184, 5399685</t>
+          <t xml:space="preserve">725773, 5151011</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F79">
-        <v>366</v>
+        <v>3374</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3981,16 +3981,16 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">725208, 5164443</t>
+          <t xml:space="preserve">8222599</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F80">
-        <v>586</v>
+        <v>2083</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4031,16 +4031,16 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">725209, 5400294</t>
+          <t xml:space="preserve">8341303</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F81">
-        <v>525</v>
+        <v>378</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4081,16 +4081,16 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">725214, 5167017</t>
+          <t xml:space="preserve">8341303</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F82">
-        <v>1751</v>
+        <v>719</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">725254, 5401425</t>
+          <t xml:space="preserve">8341303</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F83">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4181,16 +4181,16 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">725293, 5162695</t>
+          <t xml:space="preserve">8341303</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F84">
-        <v>440</v>
+        <v>1316</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4231,16 +4231,16 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">725364, 5159745</t>
+          <t xml:space="preserve">8348162</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F85">
-        <v>262</v>
+        <v>1060</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4281,16 +4281,16 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">725513, 5408522</t>
+          <t xml:space="preserve">8348162</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F86">
-        <v>421</v>
+        <v>531</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4331,16 +4331,16 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">725541, 5409688</t>
+          <t xml:space="preserve">8348162</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F87">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">725542, 5409686</t>
+          <t xml:space="preserve">8348282</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="F88">
-        <v>363</v>
+        <v>399</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4431,16 +4431,16 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">725544, 5409689</t>
+          <t xml:space="preserve">8348282</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F89">
-        <v>1526</v>
+        <v>351</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4481,16 +4481,16 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">725553, 5146977</t>
+          <t xml:space="preserve">8348282</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F90">
-        <v>998</v>
+        <v>328</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4531,16 +4531,16 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">725622, 5397851</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F91">
-        <v>4070</v>
+        <v>695</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4581,16 +4581,16 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">725657, 5153397</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F92">
-        <v>378</v>
+        <v>321</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4631,16 +4631,16 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">725741, 5397656</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F93">
-        <v>1771</v>
+        <v>619</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4681,16 +4681,16 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">725773, 5151011</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F94">
-        <v>3374</v>
+        <v>576</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4731,16 +4731,16 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">725965, 8543660</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F95">
-        <v>255</v>
+        <v>343</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4781,16 +4781,16 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8222599</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F96">
-        <v>2083</v>
+        <v>665</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4831,16 +4831,16 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">8341303</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F97">
-        <v>378</v>
+        <v>486</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4881,16 +4881,16 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8341303</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F98">
-        <v>719</v>
+        <v>512</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8341303</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4940,7 +4940,7 @@
         </is>
       </c>
       <c r="F99">
-        <v>497</v>
+        <v>425</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">8341303</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="F100">
-        <v>1316</v>
+        <v>271</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348162</t>
+          <t xml:space="preserve">8369700</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F101">
-        <v>1060</v>
+        <v>356</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5081,16 +5081,16 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348162</t>
+          <t xml:space="preserve">8369700</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F102">
-        <v>531</v>
+        <v>299</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5131,16 +5131,16 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348162</t>
+          <t xml:space="preserve">8369700</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F103">
-        <v>538</v>
+        <v>1368</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5181,16 +5181,16 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348282</t>
+          <t xml:space="preserve">9126524</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F104">
-        <v>399</v>
+        <v>275</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5231,16 +5231,16 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348282</t>
+          <t xml:space="preserve">9801350</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F105">
-        <v>351</v>
+        <v>294</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5281,16 +5281,16 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348282</t>
+          <t xml:space="preserve">9801350</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F106">
-        <v>328</v>
+        <v>428</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">9917473</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5340,7 +5340,7 @@
         </is>
       </c>
       <c r="F107">
-        <v>695</v>
+        <v>1778</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">9917473</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F108">
-        <v>321</v>
+        <v>1398</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5431,16 +5431,16 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">9917473</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F109">
-        <v>619</v>
+        <v>573</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">9917473</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F110">
-        <v>576</v>
+        <v>843</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5531,30 +5531,30 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">5407630</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F111">
-        <v>343</v>
+        <v>869</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010928</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-25</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -5581,30 +5581,30 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">5407630</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F112">
-        <v>665</v>
+        <v>450</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010928</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-25</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -5631,30 +5631,30 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">9126524</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F113">
-        <v>486</v>
+        <v>303</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200031179</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-05-06</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -5681,30 +5681,30 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">9126524</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F114">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200031179</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-05-06</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">5406207</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5740,21 +5740,21 @@
         </is>
       </c>
       <c r="F115">
-        <v>425</v>
+        <v>368</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200033154</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-06-28</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5781,30 +5781,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">7255632</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F116">
-        <v>271</v>
+        <v>4011</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200033111</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-06-28</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -5831,30 +5831,30 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369700</t>
+          <t xml:space="preserve">5409339</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F117">
-        <v>356</v>
+        <v>266</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200033230</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-06-29</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -5881,30 +5881,30 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369700</t>
+          <t xml:space="preserve">5409437</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F118">
-        <v>299</v>
+        <v>1425</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200033226</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-06-29</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -5931,30 +5931,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369700</t>
+          <t xml:space="preserve">5412912</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F119">
-        <v>1368</v>
+        <v>448</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200033225</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-06-29</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -5981,30 +5981,30 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9126524</t>
+          <t xml:space="preserve">5405376</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F120">
-        <v>275</v>
+        <v>1198</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200033676</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-07-07</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6031,30 +6031,30 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9801350</t>
+          <t xml:space="preserve">5407784</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F121">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200033685</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-07-07</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9801350</t>
+          <t xml:space="preserve">5405178</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6090,21 +6090,21 @@
         </is>
       </c>
       <c r="F122">
-        <v>428</v>
+        <v>253</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200033707</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9917473</t>
+          <t xml:space="preserve">5405374</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6140,21 +6140,21 @@
         </is>
       </c>
       <c r="F123">
-        <v>1778</v>
+        <v>478</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200033718</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6181,30 +6181,30 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9917473</t>
+          <t xml:space="preserve">5405624</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F124">
-        <v>1398</v>
+        <v>1065</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200034925</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-08-05</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -6231,30 +6231,30 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9917473</t>
+          <t xml:space="preserve">8341351</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F125">
-        <v>573</v>
+        <v>455</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200035071</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-08-10</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -6281,30 +6281,30 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9917473</t>
+          <t xml:space="preserve">10234466</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F126">
-        <v>843</v>
+        <v>1163</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200035122</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-08-11</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -6331,25 +6331,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407630</t>
+          <t xml:space="preserve">10234466</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F127">
-        <v>869</v>
+        <v>432</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010928</t>
+          <t xml:space="preserve">200035251</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-25</t>
+          <t xml:space="preserve">2020-08-13</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,25 +6381,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407630</t>
+          <t xml:space="preserve">5411731</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F128">
-        <v>450</v>
+        <v>392</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010928</t>
+          <t xml:space="preserve">200035229</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-25</t>
+          <t xml:space="preserve">2020-08-13</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9126524</t>
+          <t xml:space="preserve">5154845</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6440,16 +6440,16 @@
         </is>
       </c>
       <c r="F129">
-        <v>303</v>
+        <v>542</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">200031179</t>
+          <t xml:space="preserve">200035679</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-06</t>
+          <t xml:space="preserve">2020-08-23</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9126524</t>
+          <t xml:space="preserve">7796420</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F130">
-        <v>505</v>
+        <v>342</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">200031179</t>
+          <t xml:space="preserve">200035849</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-06</t>
+          <t xml:space="preserve">2020-08-26</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,25 +6531,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5406207</t>
+          <t xml:space="preserve">5413572</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F131">
-        <v>368</v>
+        <v>501</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033154</t>
+          <t xml:space="preserve">200035928</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-28</t>
+          <t xml:space="preserve">2020-08-27</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255632</t>
+          <t xml:space="preserve">5402389</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F132">
-        <v>4011</v>
+        <v>963</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033111</t>
+          <t xml:space="preserve">200036026</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-28</t>
+          <t xml:space="preserve">2020-08-30</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409339</t>
+          <t xml:space="preserve">5411692</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6640,16 +6640,16 @@
         </is>
       </c>
       <c r="F133">
-        <v>266</v>
+        <v>956</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033230</t>
+          <t xml:space="preserve">200036205</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-29</t>
+          <t xml:space="preserve">2020-09-01</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,25 +6681,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409437</t>
+          <t xml:space="preserve">10234466</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F134">
-        <v>1425</v>
+        <v>2517</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033226</t>
+          <t xml:space="preserve">200036384</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-29</t>
+          <t xml:space="preserve">2020-09-02</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5412912</t>
+          <t xml:space="preserve">5411642</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F135">
-        <v>448</v>
+        <v>1177</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033225</t>
+          <t xml:space="preserve">200036366</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-29</t>
+          <t xml:space="preserve">2020-09-02</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405376</t>
+          <t xml:space="preserve">5413395</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6790,16 +6790,16 @@
         </is>
       </c>
       <c r="F136">
-        <v>1198</v>
+        <v>300</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033676</t>
+          <t xml:space="preserve">200036309</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-07</t>
+          <t xml:space="preserve">2020-09-02</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,25 +6831,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407784</t>
+          <t xml:space="preserve">5413433</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F137">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033685</t>
+          <t xml:space="preserve">200036397</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-07</t>
+          <t xml:space="preserve">2020-09-03</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405374</t>
+          <t xml:space="preserve">5402452</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="F138">
-        <v>478</v>
+        <v>317</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033718</t>
+          <t xml:space="preserve">200036509</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-09-06</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405624</t>
+          <t xml:space="preserve">5402005</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6940,16 +6940,16 @@
         </is>
       </c>
       <c r="F139">
-        <v>1065</v>
+        <v>251</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034925</t>
+          <t xml:space="preserve">200036613</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-05</t>
+          <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8341351</t>
+          <t xml:space="preserve">5403146</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6990,16 +6990,16 @@
         </is>
       </c>
       <c r="F140">
-        <v>455</v>
+        <v>308</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034911</t>
+          <t xml:space="preserve">200036610</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-05</t>
+          <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">10234466</t>
+          <t xml:space="preserve">5146874</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F141">
-        <v>1163</v>
+        <v>2460</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035122</t>
+          <t xml:space="preserve">200037100</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-11</t>
+          <t xml:space="preserve">2020-09-15</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">10234466</t>
+          <t xml:space="preserve">5147263</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F142">
-        <v>432</v>
+        <v>1243</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035251</t>
+          <t xml:space="preserve">200037111</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-13</t>
+          <t xml:space="preserve">2020-09-15</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411731</t>
+          <t xml:space="preserve">5407230</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7140,16 +7140,16 @@
         </is>
       </c>
       <c r="F143">
-        <v>392</v>
+        <v>734</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035229</t>
+          <t xml:space="preserve">200037141</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-13</t>
+          <t xml:space="preserve">2020-09-15</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5154845</t>
+          <t xml:space="preserve">5146394</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7190,16 +7190,16 @@
         </is>
       </c>
       <c r="F144">
-        <v>542</v>
+        <v>1972</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035679</t>
+          <t xml:space="preserve">200038288</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-23</t>
+          <t xml:space="preserve">2020-10-01</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7796420</t>
+          <t xml:space="preserve">5407924</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7240,16 +7240,16 @@
         </is>
       </c>
       <c r="F145">
-        <v>342</v>
+        <v>612</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035849</t>
+          <t xml:space="preserve">200038276</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-26</t>
+          <t xml:space="preserve">2020-10-01</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5413572</t>
+          <t xml:space="preserve">5158331</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7290,16 +7290,16 @@
         </is>
       </c>
       <c r="F146">
-        <v>501</v>
+        <v>278</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035928</t>
+          <t xml:space="preserve">200038401</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-27</t>
+          <t xml:space="preserve">2020-10-04</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,25 +7331,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402389</t>
+          <t xml:space="preserve">5397680</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F147">
-        <v>963</v>
+        <v>772</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036026</t>
+          <t xml:space="preserve">200038484</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-30</t>
+          <t xml:space="preserve">2020-10-05</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411692</t>
+          <t xml:space="preserve">5397680</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F148">
-        <v>956</v>
+        <v>347</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036205</t>
+          <t xml:space="preserve">200038484</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-01</t>
+          <t xml:space="preserve">2020-10-05</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">10234466</t>
+          <t xml:space="preserve">5397680</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F149">
-        <v>2517</v>
+        <v>1306</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036384</t>
+          <t xml:space="preserve">200038484</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-02</t>
+          <t xml:space="preserve">2020-10-05</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411642</t>
+          <t xml:space="preserve">5397680</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F150">
-        <v>1177</v>
+        <v>820</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036366</t>
+          <t xml:space="preserve">200038484</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-02</t>
+          <t xml:space="preserve">2020-10-05</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5413395</t>
+          <t xml:space="preserve">5397250</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7544,12 +7544,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036309</t>
+          <t xml:space="preserve">100187070</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-02</t>
+          <t xml:space="preserve">2020-10-11</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5413433</t>
+          <t xml:space="preserve">5398447</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7590,16 +7590,16 @@
         </is>
       </c>
       <c r="F152">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036397</t>
+          <t xml:space="preserve">200038941</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-03</t>
+          <t xml:space="preserve">2020-10-12</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402452</t>
+          <t xml:space="preserve">5410241</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -7640,16 +7640,16 @@
         </is>
       </c>
       <c r="F153">
-        <v>317</v>
+        <v>3649</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036509</t>
+          <t xml:space="preserve">200038976</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-06</t>
+          <t xml:space="preserve">2020-10-12</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,25 +7681,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402005</t>
+          <t xml:space="preserve">7636485</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F154">
-        <v>251</v>
+        <v>991</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036613</t>
+          <t xml:space="preserve">200039035</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-07</t>
+          <t xml:space="preserve">2020-10-13</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403146</t>
+          <t xml:space="preserve">5162734</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -7740,16 +7740,16 @@
         </is>
       </c>
       <c r="F155">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036610</t>
+          <t xml:space="preserve">200039090</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-07</t>
+          <t xml:space="preserve">2020-10-14</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">288308, 288309</t>
+          <t xml:space="preserve">5409944</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="F156">
-        <v>2282</v>
+        <v>468</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037152</t>
+          <t xml:space="preserve">200039135</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-15</t>
+          <t xml:space="preserve">2020-10-14</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146874</t>
+          <t xml:space="preserve">7255632</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7840,16 +7840,16 @@
         </is>
       </c>
       <c r="F157">
-        <v>2460</v>
+        <v>2346</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037100</t>
+          <t xml:space="preserve">200039139</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-15</t>
+          <t xml:space="preserve">2020-10-14</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5147263</t>
+          <t xml:space="preserve">5162690</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -7890,16 +7890,16 @@
         </is>
       </c>
       <c r="F158">
-        <v>1243</v>
+        <v>619</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037111</t>
+          <t xml:space="preserve">200039409</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-15</t>
+          <t xml:space="preserve">2020-10-19</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407230</t>
+          <t xml:space="preserve">5165482</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="F159">
-        <v>734</v>
+        <v>395</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037141</t>
+          <t xml:space="preserve">200039408</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-15</t>
+          <t xml:space="preserve">2020-10-19</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146394</t>
+          <t xml:space="preserve">5400670</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7990,16 +7990,16 @@
         </is>
       </c>
       <c r="F160">
-        <v>1972</v>
+        <v>276</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038288</t>
+          <t xml:space="preserve">200039667</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-01</t>
+          <t xml:space="preserve">2020-10-24</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407924</t>
+          <t xml:space="preserve">5398315</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8040,16 +8040,16 @@
         </is>
       </c>
       <c r="F161">
-        <v>612</v>
+        <v>809</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038276</t>
+          <t xml:space="preserve">200039670</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-01</t>
+          <t xml:space="preserve">2020-10-25</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5158331</t>
+          <t xml:space="preserve">5400565</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="F162">
-        <v>278</v>
+        <v>605</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038401</t>
+          <t xml:space="preserve">200039746</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-04</t>
+          <t xml:space="preserve">2020-10-26</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">288458, 288459</t>
+          <t xml:space="preserve">5404249</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8140,16 +8140,16 @@
         </is>
       </c>
       <c r="F163">
-        <v>1231</v>
+        <v>2869</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038748</t>
+          <t xml:space="preserve">200039729</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-08</t>
+          <t xml:space="preserve">2020-10-26</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397250</t>
+          <t xml:space="preserve">5397138</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8190,16 +8190,16 @@
         </is>
       </c>
       <c r="F164">
-        <v>300</v>
+        <v>1368</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">100187070</t>
+          <t xml:space="preserve">200039896</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-11</t>
+          <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5398447</t>
+          <t xml:space="preserve">5411634</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8240,16 +8240,16 @@
         </is>
       </c>
       <c r="F165">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038941</t>
+          <t xml:space="preserve">200039822</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-12</t>
+          <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410241</t>
+          <t xml:space="preserve">5411636</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -8290,16 +8290,16 @@
         </is>
       </c>
       <c r="F166">
-        <v>3649</v>
+        <v>293</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038976</t>
+          <t xml:space="preserve">200039828</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-12</t>
+          <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">7636485</t>
+          <t xml:space="preserve">5411643</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F167">
-        <v>991</v>
+        <v>4582</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039035</t>
+          <t xml:space="preserve">200039847</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-13</t>
+          <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5162734</t>
+          <t xml:space="preserve">7370629</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8390,16 +8390,16 @@
         </is>
       </c>
       <c r="F168">
-        <v>360</v>
+        <v>1857</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039090</t>
+          <t xml:space="preserve">200039835</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-14</t>
+          <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409944</t>
+          <t xml:space="preserve">8222599</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8440,16 +8440,16 @@
         </is>
       </c>
       <c r="F169">
-        <v>468</v>
+        <v>384</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039135</t>
+          <t xml:space="preserve">200039808</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-14</t>
+          <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255632</t>
+          <t xml:space="preserve">8348162</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8490,16 +8490,16 @@
         </is>
       </c>
       <c r="F170">
-        <v>2346</v>
+        <v>423</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039139</t>
+          <t xml:space="preserve">200039893</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-14</t>
+          <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5162690</t>
+          <t xml:space="preserve">5162695</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F171">
-        <v>619</v>
+        <v>1555</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039409</t>
+          <t xml:space="preserve">200040823</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-19</t>
+          <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5165482</t>
+          <t xml:space="preserve">5164440</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F172">
-        <v>395</v>
+        <v>2054</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039408</t>
+          <t xml:space="preserve">200040831</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-19</t>
+          <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5398315</t>
+          <t xml:space="preserve">5164440</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F173">
-        <v>809</v>
+        <v>367</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039670</t>
+          <t xml:space="preserve">200040831</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-25</t>
+          <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400565</t>
+          <t xml:space="preserve">5401681</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="F174">
-        <v>605</v>
+        <v>4130</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039746</t>
+          <t xml:space="preserve">200040820</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-26</t>
+          <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,25 +8731,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404249</t>
+          <t xml:space="preserve">725293, 5162695</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F175">
-        <v>2869</v>
+        <v>440</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039729</t>
+          <t xml:space="preserve">200040823</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-26</t>
+          <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397138</t>
+          <t xml:space="preserve">8348282</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -8790,16 +8790,16 @@
         </is>
       </c>
       <c r="F176">
-        <v>1368</v>
+        <v>822</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039896</t>
+          <t xml:space="preserve">200040832</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-27</t>
+          <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411634</t>
+          <t xml:space="preserve">8359771</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -8840,16 +8840,16 @@
         </is>
       </c>
       <c r="F177">
-        <v>337</v>
+        <v>1439</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039822</t>
+          <t xml:space="preserve">200040821</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-27</t>
+          <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411636</t>
+          <t xml:space="preserve">5164475</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8890,16 +8890,16 @@
         </is>
       </c>
       <c r="F178">
-        <v>293</v>
+        <v>2346</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039828</t>
+          <t xml:space="preserve">200040869</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-27</t>
+          <t xml:space="preserve">2020-11-11</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411643</t>
+          <t xml:space="preserve">7118089</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -8940,16 +8940,16 @@
         </is>
       </c>
       <c r="F179">
-        <v>4582</v>
+        <v>1265</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039847</t>
+          <t xml:space="preserve">200040899</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-27</t>
+          <t xml:space="preserve">2020-11-11</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">7370629</t>
+          <t xml:space="preserve">7118089</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F180">
-        <v>1857</v>
+        <v>960</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039835</t>
+          <t xml:space="preserve">200040903</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-27</t>
+          <t xml:space="preserve">2020-11-11</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">8222599</t>
+          <t xml:space="preserve">8359765</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -9040,16 +9040,16 @@
         </is>
       </c>
       <c r="F181">
-        <v>384</v>
+        <v>2569</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039808</t>
+          <t xml:space="preserve">200040860</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-27</t>
+          <t xml:space="preserve">2020-11-11</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348162</t>
+          <t xml:space="preserve">8359765</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F182">
-        <v>423</v>
+        <v>735</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039893</t>
+          <t xml:space="preserve">200040860</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-27</t>
+          <t xml:space="preserve">2020-11-11</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5401681</t>
+          <t xml:space="preserve">7370629</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F183">
-        <v>4130</v>
+        <v>520</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040820</t>
+          <t xml:space="preserve">200047438</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-10</t>
+          <t xml:space="preserve">2021-03-31</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348282</t>
+          <t xml:space="preserve">5152207</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -9190,16 +9190,16 @@
         </is>
       </c>
       <c r="F184">
-        <v>822</v>
+        <v>351</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040832</t>
+          <t xml:space="preserve">200047661</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-10</t>
+          <t xml:space="preserve">2021-04-05</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">8359771</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -9240,16 +9240,16 @@
         </is>
       </c>
       <c r="F185">
-        <v>1439</v>
+        <v>927</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040821</t>
+          <t xml:space="preserve">200048591</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-10</t>
+          <t xml:space="preserve">2021-04-29</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5164475</t>
+          <t xml:space="preserve">5149826</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -9290,16 +9290,16 @@
         </is>
       </c>
       <c r="F186">
-        <v>2346</v>
+        <v>1532</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040869</t>
+          <t xml:space="preserve">200051851</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-11</t>
+          <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">7118089</t>
+          <t xml:space="preserve">5150673</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -9340,16 +9340,16 @@
         </is>
       </c>
       <c r="F187">
-        <v>1265</v>
+        <v>2393</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040899</t>
+          <t xml:space="preserve">200051848</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-11</t>
+          <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,25 +9381,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">7118089</t>
+          <t xml:space="preserve">5396503</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F188">
-        <v>960</v>
+        <v>820</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040903</t>
+          <t xml:space="preserve">200051846</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-11</t>
+          <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9431,25 +9431,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">8359765</t>
+          <t xml:space="preserve">5397680</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F189">
-        <v>2569</v>
+        <v>769</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040860</t>
+          <t xml:space="preserve">200051845</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-11</t>
+          <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9481,25 +9481,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">8359765</t>
+          <t xml:space="preserve">8263845</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F190">
-        <v>735</v>
+        <v>3794</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040860</t>
+          <t xml:space="preserve">200051850</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-11</t>
+          <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9531,25 +9531,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">7370629</t>
+          <t xml:space="preserve">8348046</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F191">
-        <v>520</v>
+        <v>1915</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047438</t>
+          <t xml:space="preserve">200051849</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-31</t>
+          <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5152207</t>
+          <t xml:space="preserve">5146695</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -9590,16 +9590,16 @@
         </is>
       </c>
       <c r="F192">
-        <v>351</v>
+        <v>670</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047661</t>
+          <t xml:space="preserve">311007000</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-05</t>
+          <t xml:space="preserve">2023-07-03</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5163605</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -9640,16 +9640,16 @@
         </is>
       </c>
       <c r="F193">
-        <v>927</v>
+        <v>1710</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">200048591</t>
+          <t xml:space="preserve">311020824</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-29</t>
+          <t xml:space="preserve">2023-10-07</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9681,25 +9681,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5149826</t>
+          <t xml:space="preserve">5407630</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F194">
-        <v>1532</v>
+        <v>282</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051851</t>
+          <t xml:space="preserve">311035115</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-11</t>
+          <t xml:space="preserve">2024-01-23</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9731,25 +9731,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5150673</t>
+          <t xml:space="preserve">5407630</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F195">
-        <v>2393</v>
+        <v>450</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051848</t>
+          <t xml:space="preserve">311035543</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-11</t>
+          <t xml:space="preserve">2024-01-27</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5396503</t>
+          <t xml:space="preserve">100063665</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -9790,16 +9790,16 @@
         </is>
       </c>
       <c r="F196">
-        <v>820</v>
+        <v>1227</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051846</t>
+          <t xml:space="preserve">311048343</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-11</t>
+          <t xml:space="preserve">2024-04-10</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9831,25 +9831,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397680</t>
+          <t xml:space="preserve">100056909</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F197">
-        <v>769</v>
+        <v>1592</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051845</t>
+          <t xml:space="preserve">311058955</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-11</t>
+          <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9881,25 +9881,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">8263845</t>
+          <t xml:space="preserve">100056909</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F198">
-        <v>3794</v>
+        <v>1592</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051850</t>
+          <t xml:space="preserve">311058967</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-11</t>
+          <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9931,25 +9931,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348046</t>
+          <t xml:space="preserve">100056909</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F199">
-        <v>1915</v>
+        <v>1592</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051849</t>
+          <t xml:space="preserve">311058958</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-11</t>
+          <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9981,25 +9981,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044374</t>
+          <t xml:space="preserve">725965, 8543660</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F200">
-        <v>699</v>
+        <v>255</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">310039658</t>
+          <t xml:space="preserve">311101751</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-05-14</t>
+          <t xml:space="preserve">2025-03-19</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044374</t>
+          <t xml:space="preserve">7006647</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -10040,16 +10040,16 @@
         </is>
       </c>
       <c r="F201">
-        <v>459</v>
+        <v>638</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">310039650</t>
+          <t xml:space="preserve">311182811</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-05-14</t>
+          <t xml:space="preserve">2026-06-13</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044374</t>
+          <t xml:space="preserve">725180, 5398549</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -10090,26 +10090,26 @@
         </is>
       </c>
       <c r="F202">
-        <v>460</v>
+        <v>1129</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">310039646</t>
+          <t xml:space="preserve">311244668</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-05-14</t>
+          <t xml:space="preserve">2027-05-02</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10131,35 +10131,35 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044374</t>
+          <t xml:space="preserve">725159, 5166867</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F203">
-        <v>384</v>
+        <v>575</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">310039648</t>
+          <t xml:space="preserve">311249329</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-05-14</t>
+          <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10181,35 +10181,35 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146695</t>
+          <t xml:space="preserve">10160985</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F204">
-        <v>670</v>
+        <v>3417</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311007000</t>
+          <t xml:space="preserve">311283506</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-07-03</t>
+          <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5163605</t>
+          <t xml:space="preserve">725208, 5164443</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -10240,26 +10240,26 @@
         </is>
       </c>
       <c r="F205">
-        <v>1710</v>
+        <v>586</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311020824</t>
+          <t xml:space="preserve">311430366</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-10-07</t>
+          <t xml:space="preserve">2030-03-27</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10281,35 +10281,35 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407630</t>
+          <t xml:space="preserve">100044374</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F206">
-        <v>282</v>
+        <v>699</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311035115</t>
+          <t xml:space="preserve">311746845</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-01-23</t>
+          <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10331,35 +10331,35 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407630</t>
+          <t xml:space="preserve">100044374</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F207">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311035543</t>
+          <t xml:space="preserve">311746845</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-01-27</t>
+          <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10381,35 +10381,35 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">100063665</t>
+          <t xml:space="preserve">100044374</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F208">
-        <v>1227</v>
+        <v>460</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311048343</t>
+          <t xml:space="preserve">311746845</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-04-10</t>
+          <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10431,35 +10431,35 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">100056909</t>
+          <t xml:space="preserve">100044374</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F209">
-        <v>1592</v>
+        <v>384</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311058955</t>
+          <t xml:space="preserve">311746845</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-06-12</t>
+          <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10481,35 +10481,35 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">100056909</t>
+          <t xml:space="preserve">5399685</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F210">
-        <v>1592</v>
+        <v>256</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311058967</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-06-12</t>
+          <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10531,35 +10531,35 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">100056909</t>
+          <t xml:space="preserve">725184, 5399685</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F211">
-        <v>1592</v>
+        <v>418</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311058958</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-06-12</t>
+          <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10581,35 +10581,35 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006647</t>
+          <t xml:space="preserve">725184, 5399685</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F212">
-        <v>638</v>
+        <v>691</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311182811</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-13</t>
+          <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">10160985</t>
+          <t xml:space="preserve">725184, 5399685</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -10640,16 +10640,16 @@
         </is>
       </c>
       <c r="F213">
-        <v>3417</v>
+        <v>618</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283506</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-13</t>
+          <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10686,15 +10686,15 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F214">
-        <v>618</v>
+        <v>694</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878991</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -10736,15 +10736,15 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F215">
-        <v>694</v>
+        <v>795</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878988</t>
+          <t xml:space="preserve">311878984</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -10786,15 +10786,15 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F216">
-        <v>795</v>
+        <v>366</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878984</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">

--- a/public/exports/26696348.xlsx
+++ b/public/exports/26696348.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snorrebakke Allé 2</t>
+          <t xml:space="preserve">Almindingensvej 23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3751</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100056909</t>
+          <t xml:space="preserve">8348162</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H2">
-        <v>5235</v>
+        <v>1060</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åkirkebyvej 25B</t>
+          <t xml:space="preserve">Almindingensvej 23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3751</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100683657</t>
+          <t xml:space="preserve">8348162</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H3">
-        <v>688</v>
+        <v>531</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åkirkebyvej 1</t>
+          <t xml:space="preserve">Almindingensvej 23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3751</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100683658</t>
+          <t xml:space="preserve">8348162</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H4">
-        <v>325</v>
+        <v>538</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pingels Alle 31</t>
+          <t xml:space="preserve">Bygaden 33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100998221</t>
+          <t xml:space="preserve">725657, 5153397</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H5">
-        <v>4643</v>
+        <v>378</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,17 +331,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 42</t>
+          <t xml:space="preserve">Byledsgade 86</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1354130</t>
+          <t xml:space="preserve">5410241</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -350,7 +350,7 @@
         </is>
       </c>
       <c r="H6">
-        <v>1289</v>
+        <v>519</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandemandsvej 1A</t>
+          <t xml:space="preserve">Byledsgade 86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">288308, 288309</t>
+          <t xml:space="preserve">5410241</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H7">
-        <v>2282</v>
+        <v>570</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydskovvej 2</t>
+          <t xml:space="preserve">Byledsgade 86</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">288458, 288459</t>
+          <t xml:space="preserve">5410241</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H8">
-        <v>1231</v>
+        <v>1447</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 5A</t>
+          <t xml:space="preserve">Byledsgade 86</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">288460</t>
+          <t xml:space="preserve">5410241</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H9">
-        <v>820</v>
+        <v>1584</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyker Hovedgade 7B</t>
+          <t xml:space="preserve">Byledsgade 86</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">501202, 501203, 5148340</t>
+          <t xml:space="preserve">5410241</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H10">
-        <v>996</v>
+        <v>384</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,26 +631,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snorrebakken 66</t>
+          <t xml:space="preserve">Byvangen 6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3790</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146394</t>
+          <t xml:space="preserve">5401340</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H11">
-        <v>465</v>
+        <v>1508</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snorrebakken 66</t>
+          <t xml:space="preserve">Damløkkevej 19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3790</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146394</t>
+          <t xml:space="preserve">725254, 5401425</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H12">
-        <v>575</v>
+        <v>499</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snorrebakken 66</t>
+          <t xml:space="preserve">Gartnervangen 4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146394</t>
+          <t xml:space="preserve">5412912</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H13">
-        <v>1069</v>
+        <v>420</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Ringvej 1</t>
+          <t xml:space="preserve">Godthåbsvej 39</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3751</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146695</t>
+          <t xml:space="preserve">5162197</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H14">
-        <v>988</v>
+        <v>411</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,17 +871,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Ringvej 1</t>
+          <t xml:space="preserve">Grønningen 3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146695</t>
+          <t xml:space="preserve">725622, 5397851</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H15">
-        <v>375</v>
+        <v>4070</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedeløkken 5</t>
+          <t xml:space="preserve">Gudhjemvej 107</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146874</t>
+          <t xml:space="preserve">5158331</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H16">
-        <v>495</v>
+        <v>272</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedeløkken 5</t>
+          <t xml:space="preserve">Hans Rømersvej 27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146874</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H17">
-        <v>1206</v>
+        <v>695</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,26 +1051,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedegårdsvej 33B</t>
+          <t xml:space="preserve">Hans Rømersvej 27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146874</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H18">
-        <v>613</v>
+        <v>321</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åkirkebyvej 136</t>
+          <t xml:space="preserve">Hans Rømersvej 27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146874</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H19">
-        <v>2030</v>
+        <v>619</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedevangen 9</t>
+          <t xml:space="preserve">Hans Rømersvej 27</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146874</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H20">
-        <v>944</v>
+        <v>576</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestermarievej 16</t>
+          <t xml:space="preserve">Hans Rømersvej 27</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5150673</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H21">
-        <v>559</v>
+        <v>343</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 7</t>
+          <t xml:space="preserve">Hans Rømersvej 27</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,16 +1301,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5152174</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H22">
-        <v>512</v>
+        <v>665</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Hans Rømersvej 27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5152174</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H23">
-        <v>778</v>
+        <v>512</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsgade 5</t>
+          <t xml:space="preserve">Hans Rømersvej 27</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,16 +1421,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5152476</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H24">
-        <v>736</v>
+        <v>425</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsgade 5</t>
+          <t xml:space="preserve">Hans Rømersvej 27</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,16 +1481,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5152476</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H25">
-        <v>778</v>
+        <v>271</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,17 +1531,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedersker Hovedgade 56</t>
+          <t xml:space="preserve">Havnen 1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5154831</t>
+          <t xml:space="preserve">725177, 5165787</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="H26">
-        <v>422</v>
+        <v>979</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melstedvej 1</t>
+          <t xml:space="preserve">Klemenskervej 61A</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5158110</t>
+          <t xml:space="preserve">725214, 5167017</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="H27">
-        <v>412</v>
+        <v>1751</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,26 +1651,26 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gudhjemvej 107</t>
+          <t xml:space="preserve">Kong Gustafsvej 10A</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5158331</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H28">
-        <v>272</v>
+        <v>595</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,26 +1711,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavsdalvej 30</t>
+          <t xml:space="preserve">Kong Gustafsvej 10A</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5160838</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H29">
-        <v>883</v>
+        <v>474</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,17 +1771,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavsdalvej 30</t>
+          <t xml:space="preserve">Kong Gustafsvej 10A</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5160838</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="H30">
-        <v>1892</v>
+        <v>904</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,26 +1831,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibevænget 6</t>
+          <t xml:space="preserve">Kong Gustafsvej 10A</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3751</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5161330</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H31">
-        <v>269</v>
+        <v>920</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,26 +1891,26 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 39</t>
+          <t xml:space="preserve">Kong Gustafsvej 10A</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3751</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5162197</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H32">
-        <v>411</v>
+        <v>827</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,26 +1951,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 40</t>
+          <t xml:space="preserve">Kong Gustafsvej 10A</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397138</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H33">
-        <v>1289</v>
+        <v>490</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,26 +2011,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 40</t>
+          <t xml:space="preserve">Kong Gustafsvej 10A</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397138</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H34">
-        <v>865</v>
+        <v>667</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,26 +2071,26 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 40</t>
+          <t xml:space="preserve">Kong Gustafsvej 10A</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397138</t>
+          <t xml:space="preserve">5403611</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H35">
-        <v>840</v>
+        <v>522</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,26 +2131,26 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kuleborgvej 10</t>
+          <t xml:space="preserve">Kong Gustafsvej 10A</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397138</t>
+          <t xml:space="preserve">8369700</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H36">
-        <v>835</v>
+        <v>1368</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,26 +2191,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvangen 6</t>
+          <t xml:space="preserve">Kuleborgvej 10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3790</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5401340</t>
+          <t xml:space="preserve">5397138</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H37">
-        <v>1508</v>
+        <v>835</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,26 +2251,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Gustafsvej 10A</t>
+          <t xml:space="preserve">Lille Madsegade 32</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5407641</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H38">
-        <v>595</v>
+        <v>300</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,26 +2311,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Gustafsvej 10A</t>
+          <t xml:space="preserve">Lindevej 5A</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">288460</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H39">
-        <v>474</v>
+        <v>820</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,26 +2371,26 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Gustafsvej 10A</t>
+          <t xml:space="preserve">Melstedvej 1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5158110</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>904</v>
+        <v>412</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,26 +2431,26 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Gustafsvej 10A</t>
+          <t xml:space="preserve">Munch Petersens Vej 2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5408398</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H41">
-        <v>920</v>
+        <v>353</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,17 +2491,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Gustafsvej 10A</t>
+          <t xml:space="preserve">Møllebakken 26</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">9126524</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="H42">
-        <v>827</v>
+        <v>275</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,26 +2551,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Gustafsvej 10A</t>
+          <t xml:space="preserve">Nordre Kystvej 7</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5408397</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>490</v>
+        <v>646</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2611,26 +2611,26 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Gustafsvej 10A</t>
+          <t xml:space="preserve">Nygade 40</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5397138</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H44">
-        <v>667</v>
+        <v>1289</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2671,26 +2671,26 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Gustafsvej 10A</t>
+          <t xml:space="preserve">Nygade 40</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403611</t>
+          <t xml:space="preserve">5397138</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H45">
-        <v>522</v>
+        <v>865</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 18</t>
+          <t xml:space="preserve">Nygade 40</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403668</t>
+          <t xml:space="preserve">5397138</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H46">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2791,26 +2791,26 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenbrudsvej 23</t>
+          <t xml:space="preserve">Nygade 42</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404014</t>
+          <t xml:space="preserve">1354130</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H47">
-        <v>1827</v>
+        <v>1289</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2851,17 +2851,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paradisvej 70</t>
+          <t xml:space="preserve">Nyker Hovedgade 7B</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404454</t>
+          <t xml:space="preserve">501202, 501203, 5148340</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="H48">
-        <v>314</v>
+        <v>996</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2911,26 +2911,26 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paradisvej 72</t>
+          <t xml:space="preserve">Otto Bruuns Plads 1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404454</t>
+          <t xml:space="preserve">8348282</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H49">
-        <v>501</v>
+        <v>399</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2971,26 +2971,26 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paradisvej 68A</t>
+          <t xml:space="preserve">Otto Bruuns Plads 1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404454</t>
+          <t xml:space="preserve">8348282</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H50">
-        <v>633</v>
+        <v>351</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3031,26 +3031,26 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paradisvej 74B</t>
+          <t xml:space="preserve">Otto Bruuns Plads 1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404454</t>
+          <t xml:space="preserve">8348282</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H51">
-        <v>732</v>
+        <v>328</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paradisvej 70</t>
+          <t xml:space="preserve">Paradisvej 68A</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3106,11 +3106,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H52">
-        <v>1652</v>
+        <v>633</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3151,26 +3151,26 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Madsegade 32</t>
+          <t xml:space="preserve">Paradisvej 70</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407641</t>
+          <t xml:space="preserve">5404454</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H53">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3211,26 +3211,26 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Kystvej 7</t>
+          <t xml:space="preserve">Paradisvej 70</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5408397</t>
+          <t xml:space="preserve">5404454</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H54">
-        <v>646</v>
+        <v>1652</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3271,26 +3271,26 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munch Petersens Vej 2</t>
+          <t xml:space="preserve">Paradisvej 72</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5408398</t>
+          <t xml:space="preserve">5404454</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H55">
-        <v>353</v>
+        <v>501</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3331,26 +3331,26 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torneværksvej 1</t>
+          <t xml:space="preserve">Paradisvej 74B</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409685</t>
+          <t xml:space="preserve">5404454</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H56">
-        <v>3052</v>
+        <v>732</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3391,26 +3391,26 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torneværksvej 1</t>
+          <t xml:space="preserve">Pedersker Hovedgade 56</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409685</t>
+          <t xml:space="preserve">5154831</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H57">
-        <v>897</v>
+        <v>422</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torneværksvej 1</t>
+          <t xml:space="preserve">Pingels Alle 31</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,16 +3461,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409685</t>
+          <t xml:space="preserve">100998221</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H58">
-        <v>290</v>
+        <v>4643</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torneværksvej 1D</t>
+          <t xml:space="preserve">Plantagevej 5B</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,16 +3521,16 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409689</t>
+          <t xml:space="preserve">9801350</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H59">
-        <v>668</v>
+        <v>428</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byledsgade 86</t>
+          <t xml:space="preserve">Plantagevej 5E</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,16 +3581,16 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410241</t>
+          <t xml:space="preserve">9801350</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H60">
-        <v>519</v>
+        <v>294</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3631,26 +3631,26 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byledsgade 86</t>
+          <t xml:space="preserve">Ravnsgade 5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410241</t>
+          <t xml:space="preserve">5152476</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>570</v>
+        <v>736</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3691,26 +3691,26 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byledsgade 86</t>
+          <t xml:space="preserve">Ravnsgade 5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410241</t>
+          <t xml:space="preserve">5152476</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H62">
-        <v>1447</v>
+        <v>778</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byledsgade 86</t>
+          <t xml:space="preserve">Remisevej 16</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,16 +3761,16 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410241</t>
+          <t xml:space="preserve">725513, 5408522</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H63">
-        <v>1584</v>
+        <v>421</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3811,26 +3811,26 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byledsgade 86</t>
+          <t xml:space="preserve">Sandlinien 5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410241</t>
+          <t xml:space="preserve">725209, 5400294</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H64">
-        <v>384</v>
+        <v>525</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3871,26 +3871,26 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gartnervangen 4</t>
+          <t xml:space="preserve">Skoleparken 5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5412912</t>
+          <t xml:space="preserve">8367855</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H65">
-        <v>420</v>
+        <v>486</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3931,26 +3931,26 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 1</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">725177, 5165787</t>
+          <t xml:space="preserve">5152174</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H66">
-        <v>979</v>
+        <v>778</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3991,26 +3991,26 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandlinien 5</t>
+          <t xml:space="preserve">Skolevej 7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">725209, 5400294</t>
+          <t xml:space="preserve">5152174</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H67">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4051,26 +4051,26 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klemenskervej 61A</t>
+          <t xml:space="preserve">Skovgårdsvejen 21B</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">725214, 5167017</t>
+          <t xml:space="preserve">725773, 5151011</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H68">
-        <v>1751</v>
+        <v>3374</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4111,26 +4111,26 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damløkkevej 19</t>
+          <t xml:space="preserve">Smedegårdsvej 33B</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3790</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">725254, 5401425</t>
+          <t xml:space="preserve">5146874</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H69">
-        <v>499</v>
+        <v>613</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4171,26 +4171,26 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandstien 1A</t>
+          <t xml:space="preserve">Smedeløkken 5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">725364, 5159745</t>
+          <t xml:space="preserve">5146874</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H70">
-        <v>262</v>
+        <v>495</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remisevej 16</t>
+          <t xml:space="preserve">Smedeløkken 5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4241,16 +4241,16 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">725513, 5408522</t>
+          <t xml:space="preserve">5146874</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H71">
-        <v>421</v>
+        <v>1206</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torneværksvej 1A</t>
+          <t xml:space="preserve">Smedevangen 9</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4301,16 +4301,16 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">725541, 5409688</t>
+          <t xml:space="preserve">5146874</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="H72">
-        <v>532</v>
+        <v>944</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torneværksvej 1B</t>
+          <t xml:space="preserve">Snorrebakke Allé 2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,16 +4361,16 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">725542, 5409686</t>
+          <t xml:space="preserve">100056909</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H73">
-        <v>363</v>
+        <v>5235</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torneværksvej 1D</t>
+          <t xml:space="preserve">Snorrebakken 66</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4421,16 +4421,16 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">725544, 5409689</t>
+          <t xml:space="preserve">5146394</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H74">
-        <v>1526</v>
+        <v>465</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åkirkebyvej 138</t>
+          <t xml:space="preserve">Snorrebakken 66</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,16 +4481,16 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">725553, 5146977</t>
+          <t xml:space="preserve">5146394</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H75">
-        <v>998</v>
+        <v>575</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4531,26 +4531,26 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 3</t>
+          <t xml:space="preserve">Snorrebakken 66</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">725622, 5397851</t>
+          <t xml:space="preserve">5146394</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H76">
-        <v>4070</v>
+        <v>1069</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4591,26 +4591,26 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 33</t>
+          <t xml:space="preserve">Stadionvej 18</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">725657, 5153397</t>
+          <t xml:space="preserve">5403668</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H77">
-        <v>378</v>
+        <v>847</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4651,26 +4651,26 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strøbyvej 1</t>
+          <t xml:space="preserve">Stadionvej 19</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">725741, 5397656</t>
+          <t xml:space="preserve">8369700</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H78">
-        <v>1771</v>
+        <v>299</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4711,26 +4711,26 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovgårdsvejen 21B</t>
+          <t xml:space="preserve">Stadionvej 21</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">725773, 5151011</t>
+          <t xml:space="preserve">8369700</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H79">
-        <v>3374</v>
+        <v>356</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4771,26 +4771,26 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenbrudsvej 43</t>
+          <t xml:space="preserve">Stavsdalvej 30</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8222599</t>
+          <t xml:space="preserve">5160838</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>2083</v>
+        <v>883</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4831,26 +4831,26 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibegårdsvej 2</t>
+          <t xml:space="preserve">Stavsdalvej 30</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8341303</t>
+          <t xml:space="preserve">5160838</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H81">
-        <v>378</v>
+        <v>1892</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4891,26 +4891,26 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibegårdsvej 5</t>
+          <t xml:space="preserve">Stenbrudsvej 23</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8341303</t>
+          <t xml:space="preserve">5404014</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H82">
-        <v>719</v>
+        <v>1827</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4951,17 +4951,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibegårdsvej 2</t>
+          <t xml:space="preserve">Stenbrudsvej 43</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8341303</t>
+          <t xml:space="preserve">8222599</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="H83">
-        <v>497</v>
+        <v>2083</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5011,17 +5011,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibegårdsvej 2</t>
+          <t xml:space="preserve">Strandstien 1A</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8341303</t>
+          <t xml:space="preserve">725364, 5159745</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="H84">
-        <v>1316</v>
+        <v>262</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5071,26 +5071,26 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Almindingensvej 23</t>
+          <t xml:space="preserve">Strandvejen 14</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3751</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348162</t>
+          <t xml:space="preserve">9917473</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H85">
-        <v>1060</v>
+        <v>1778</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -5131,26 +5131,26 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Almindingensvej 23</t>
+          <t xml:space="preserve">Strandvejen 14</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3751</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348162</t>
+          <t xml:space="preserve">9917473</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H86">
-        <v>531</v>
+        <v>1398</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5191,17 +5191,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Almindingensvej 23</t>
+          <t xml:space="preserve">Strandvejen 14</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3751</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348162</t>
+          <t xml:space="preserve">9917473</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="H87">
-        <v>538</v>
+        <v>573</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5251,26 +5251,26 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otto Bruuns Plads 1</t>
+          <t xml:space="preserve">Strandvejen 14</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348282</t>
+          <t xml:space="preserve">9917473</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H88">
-        <v>399</v>
+        <v>843</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5311,26 +5311,26 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otto Bruuns Plads 1</t>
+          <t xml:space="preserve">Strøbyvej 1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348282</t>
+          <t xml:space="preserve">725741, 5397656</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>351</v>
+        <v>1771</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5371,26 +5371,26 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otto Bruuns Plads 1</t>
+          <t xml:space="preserve">Torneværksvej 1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348282</t>
+          <t xml:space="preserve">5409685</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H90">
-        <v>328</v>
+        <v>3052</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -5431,26 +5431,26 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Rømersvej 27</t>
+          <t xml:space="preserve">Torneværksvej 1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">5409685</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H91">
-        <v>695</v>
+        <v>897</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5491,26 +5491,26 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Rømersvej 27</t>
+          <t xml:space="preserve">Torneværksvej 1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">5409685</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H92">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5551,26 +5551,26 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Rømersvej 27</t>
+          <t xml:space="preserve">Torneværksvej 1A</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">725541, 5409688</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H93">
-        <v>619</v>
+        <v>532</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5611,26 +5611,26 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Rømersvej 27</t>
+          <t xml:space="preserve">Torneværksvej 1B</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">725542, 5409686</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H94">
-        <v>576</v>
+        <v>363</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5671,26 +5671,26 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Rømersvej 27</t>
+          <t xml:space="preserve">Torneværksvej 1D</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">5409689</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H95">
-        <v>343</v>
+        <v>668</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5731,26 +5731,26 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Rømersvej 27</t>
+          <t xml:space="preserve">Torneværksvej 1D</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">725544, 5409689</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H96">
-        <v>665</v>
+        <v>1526</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5791,26 +5791,26 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoleparken 5</t>
+          <t xml:space="preserve">Vestermarievej 16</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">5150673</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H97">
-        <v>486</v>
+        <v>559</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5851,26 +5851,26 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Rømersvej 27</t>
+          <t xml:space="preserve">Vibegårdsvej 2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">8341303</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H98">
-        <v>512</v>
+        <v>378</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5911,17 +5911,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Rømersvej 27</t>
+          <t xml:space="preserve">Vibegårdsvej 2</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">8341303</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="H99">
-        <v>425</v>
+        <v>497</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5971,17 +5971,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Rømersvej 27</t>
+          <t xml:space="preserve">Vibegårdsvej 2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367855</t>
+          <t xml:space="preserve">8341303</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="H100">
-        <v>271</v>
+        <v>1316</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6031,26 +6031,26 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 21</t>
+          <t xml:space="preserve">Vibegårdsvej 5</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369700</t>
+          <t xml:space="preserve">8341303</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H101">
-        <v>356</v>
+        <v>719</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6091,26 +6091,26 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 19</t>
+          <t xml:space="preserve">Vibevænget 6</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3751</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369700</t>
+          <t xml:space="preserve">5161330</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H102">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6151,26 +6151,26 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Gustafsvej 10A</t>
+          <t xml:space="preserve">Åkirkebyvej 1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369700</t>
+          <t xml:space="preserve">100683658</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H103">
-        <v>1368</v>
+        <v>325</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6211,26 +6211,26 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebakken 26</t>
+          <t xml:space="preserve">Åkirkebyvej 136</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9126524</t>
+          <t xml:space="preserve">5146874</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H104">
-        <v>275</v>
+        <v>2030</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 5E</t>
+          <t xml:space="preserve">Åkirkebyvej 138</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6281,16 +6281,16 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9801350</t>
+          <t xml:space="preserve">725553, 5146977</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="H105">
-        <v>294</v>
+        <v>998</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 5B</t>
+          <t xml:space="preserve">Åkirkebyvej 25B</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6341,16 +6341,16 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9801350</t>
+          <t xml:space="preserve">100683657</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H106">
-        <v>428</v>
+        <v>688</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6391,26 +6391,26 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 14</t>
+          <t xml:space="preserve">Østre Ringvej 1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9917473</t>
+          <t xml:space="preserve">5146695</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H107">
-        <v>1778</v>
+        <v>988</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -6451,26 +6451,26 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 14</t>
+          <t xml:space="preserve">Østre Ringvej 1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">9917473</t>
+          <t xml:space="preserve">5146695</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H108">
-        <v>1398</v>
+        <v>375</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -6511,40 +6511,40 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 14</t>
+          <t xml:space="preserve">Stenbanen 18</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9917473</t>
+          <t xml:space="preserve">5407630</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H109">
-        <v>573</v>
+        <v>869</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010928</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-25</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -6571,40 +6571,40 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 14</t>
+          <t xml:space="preserve">Stenbanen 24</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">9917473</t>
+          <t xml:space="preserve">5407630</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H110">
-        <v>843</v>
+        <v>450</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010928</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-25</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6631,17 +6631,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenbanen 18</t>
+          <t xml:space="preserve">Møllebakken 26</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407630</t>
+          <t xml:space="preserve">9126524</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6650,16 +6650,16 @@
         </is>
       </c>
       <c r="H111">
-        <v>869</v>
+        <v>303</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010928</t>
+          <t xml:space="preserve">200031179</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-25</t>
+          <t xml:space="preserve">2020-05-06</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,17 +6691,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenbanen 24</t>
+          <t xml:space="preserve">Møllebakken 28</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407630</t>
+          <t xml:space="preserve">9126524</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6710,16 +6710,16 @@
         </is>
       </c>
       <c r="H112">
-        <v>450</v>
+        <v>505</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010928</t>
+          <t xml:space="preserve">200031179</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-25</t>
+          <t xml:space="preserve">2020-05-06</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,35 +6751,35 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebakken 26</t>
+          <t xml:space="preserve">Landemærket 26</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">9126524</t>
+          <t xml:space="preserve">7255632</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H113">
-        <v>303</v>
+        <v>4011</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">200031179</t>
+          <t xml:space="preserve">200033111</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-06</t>
+          <t xml:space="preserve">2020-06-28</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6811,17 +6811,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebakken 28</t>
+          <t xml:space="preserve">Marie Kofoeds Vej 7</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9126524</t>
+          <t xml:space="preserve">5406207</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6830,16 +6830,16 @@
         </is>
       </c>
       <c r="H114">
-        <v>505</v>
+        <v>368</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">200031179</t>
+          <t xml:space="preserve">200033154</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-06</t>
+          <t xml:space="preserve">2020-06-28</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marie Kofoeds Vej 7</t>
+          <t xml:space="preserve">Gartnervangen 4</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5406207</t>
+          <t xml:space="preserve">5412912</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H115">
-        <v>368</v>
+        <v>448</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033154</t>
+          <t xml:space="preserve">200033225</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-28</t>
+          <t xml:space="preserve">2020-06-29</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landemærket 26</t>
+          <t xml:space="preserve">Haslevej 64</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6941,25 +6941,25 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255632</t>
+          <t xml:space="preserve">5409339</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H116">
-        <v>4011</v>
+        <v>266</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033151</t>
+          <t xml:space="preserve">200033230</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-28</t>
+          <t xml:space="preserve">2020-06-29</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haslevej 64</t>
+          <t xml:space="preserve">Sveasvej 8</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409339</t>
+          <t xml:space="preserve">5409437</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7010,11 +7010,11 @@
         </is>
       </c>
       <c r="H117">
-        <v>266</v>
+        <v>1425</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033230</t>
+          <t xml:space="preserve">200033226</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sveasvej 8</t>
+          <t xml:space="preserve">Dampmøllegade 36</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7061,25 +7061,25 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409437</t>
+          <t xml:space="preserve">5407784</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H118">
-        <v>1425</v>
+        <v>311</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033226</t>
+          <t xml:space="preserve">200033685</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-29</t>
+          <t xml:space="preserve">2020-07-07</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gartnervangen 4</t>
+          <t xml:space="preserve">Østergade 54</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5412912</t>
+          <t xml:space="preserve">5405376</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7130,16 +7130,16 @@
         </is>
       </c>
       <c r="H119">
-        <v>448</v>
+        <v>1198</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033225</t>
+          <t xml:space="preserve">200033676</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-29</t>
+          <t xml:space="preserve">2020-07-07</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 54</t>
+          <t xml:space="preserve">Løkkegade 15A</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405376</t>
+          <t xml:space="preserve">5405178</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H120">
-        <v>1198</v>
+        <v>253</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033676</t>
+          <t xml:space="preserve">200033707</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-07</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dampmøllegade 36</t>
+          <t xml:space="preserve">Østergade 50</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7241,25 +7241,25 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407784</t>
+          <t xml:space="preserve">5405374</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H121">
-        <v>311</v>
+        <v>478</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033685</t>
+          <t xml:space="preserve">200033718</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-07</t>
+          <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løkkegade 15A</t>
+          <t xml:space="preserve">Sankt Mortens Gade 33</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,25 +7301,25 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405178</t>
+          <t xml:space="preserve">5405624</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H122">
-        <v>253</v>
+        <v>1065</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033707</t>
+          <t xml:space="preserve">200034925</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-08-05</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 50</t>
+          <t xml:space="preserve">Ullasvej 5</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405374</t>
+          <t xml:space="preserve">8341351</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7370,16 +7370,16 @@
         </is>
       </c>
       <c r="H123">
-        <v>478</v>
+        <v>455</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033718</t>
+          <t xml:space="preserve">200035071</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-08</t>
+          <t xml:space="preserve">2020-08-10</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Mortens Gade 33</t>
+          <t xml:space="preserve">Ullasvej 43</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7421,25 +7421,25 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5405624</t>
+          <t xml:space="preserve">10234466</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="H124">
-        <v>1065</v>
+        <v>1163</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034925</t>
+          <t xml:space="preserve">200035122</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-05</t>
+          <t xml:space="preserve">2020-08-11</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullasvej 5</t>
+          <t xml:space="preserve">Helsevej 4</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8341351</t>
+          <t xml:space="preserve">10234466</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H125">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035073</t>
+          <t xml:space="preserve">200035251</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-10</t>
+          <t xml:space="preserve">2020-08-13</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullasvej 43</t>
+          <t xml:space="preserve">Sagavej 19</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7541,25 +7541,25 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">10234466</t>
+          <t xml:space="preserve">5411731</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H126">
-        <v>1163</v>
+        <v>392</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035122</t>
+          <t xml:space="preserve">200035229</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-11</t>
+          <t xml:space="preserve">2020-08-13</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,35 +7591,35 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helsevej 4</t>
+          <t xml:space="preserve">Pedersker Hovedgade 46</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">10234466</t>
+          <t xml:space="preserve">5154845</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H127">
-        <v>432</v>
+        <v>542</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035251</t>
+          <t xml:space="preserve">200035679</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-13</t>
+          <t xml:space="preserve">2020-08-23</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sagavej 19</t>
+          <t xml:space="preserve">Skippergade 8</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411731</t>
+          <t xml:space="preserve">7796420</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7670,16 +7670,16 @@
         </is>
       </c>
       <c r="H128">
-        <v>392</v>
+        <v>342</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035250</t>
+          <t xml:space="preserve">200035849</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-13</t>
+          <t xml:space="preserve">2020-08-26</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,17 +7711,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedersker Hovedgade 46</t>
+          <t xml:space="preserve">Storegade 24</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5154845</t>
+          <t xml:space="preserve">5413572</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -7730,16 +7730,16 @@
         </is>
       </c>
       <c r="H129">
-        <v>542</v>
+        <v>501</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035679</t>
+          <t xml:space="preserve">200035928</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-23</t>
+          <t xml:space="preserve">2020-08-27</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7771,17 +7771,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skippergade 8</t>
+          <t xml:space="preserve">Kildestræde 18</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">7796420</t>
+          <t xml:space="preserve">5402389</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="H130">
-        <v>342</v>
+        <v>963</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035849</t>
+          <t xml:space="preserve">200036026</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-26</t>
+          <t xml:space="preserve">2020-08-30</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,17 +7831,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 24</t>
+          <t xml:space="preserve">Sagavej 2</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5413572</t>
+          <t xml:space="preserve">5411692</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -7850,16 +7850,16 @@
         </is>
       </c>
       <c r="H131">
-        <v>501</v>
+        <v>956</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035928</t>
+          <t xml:space="preserve">200036205</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-27</t>
+          <t xml:space="preserve">2020-09-01</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,17 +7891,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildestræde 18</t>
+          <t xml:space="preserve">Brænderigænget 10</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402389</t>
+          <t xml:space="preserve">5413395</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7910,16 +7910,16 @@
         </is>
       </c>
       <c r="H132">
-        <v>963</v>
+        <v>300</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036026</t>
+          <t xml:space="preserve">200036309</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-30</t>
+          <t xml:space="preserve">2020-09-02</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sagavej 2</t>
+          <t xml:space="preserve">Ullasvej 17</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7961,25 +7961,25 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411692</t>
+          <t xml:space="preserve">5411642</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H133">
-        <v>956</v>
+        <v>1177</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036205</t>
+          <t xml:space="preserve">200036366</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-01</t>
+          <t xml:space="preserve">2020-09-02</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8071,35 +8071,35 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullasvej 17</t>
+          <t xml:space="preserve">Borgergade 4</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411642</t>
+          <t xml:space="preserve">5413433</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H135">
-        <v>1177</v>
+        <v>336</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036366</t>
+          <t xml:space="preserve">200036397</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-02</t>
+          <t xml:space="preserve">2020-09-03</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8131,17 +8131,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brænderigænget 10</t>
+          <t xml:space="preserve">Damgade 10B</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5413395</t>
+          <t xml:space="preserve">5402452</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8150,16 +8150,16 @@
         </is>
       </c>
       <c r="H136">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036309</t>
+          <t xml:space="preserve">200036509</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-02</t>
+          <t xml:space="preserve">2020-09-06</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8191,17 +8191,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 4</t>
+          <t xml:space="preserve">Havnen 9</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5413433</t>
+          <t xml:space="preserve">5403146</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8210,16 +8210,16 @@
         </is>
       </c>
       <c r="H137">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036397</t>
+          <t xml:space="preserve">200036610</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-03</t>
+          <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damgade 10B</t>
+          <t xml:space="preserve">Munkegade 18A</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402452</t>
+          <t xml:space="preserve">5402005</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8270,16 +8270,16 @@
         </is>
       </c>
       <c r="H138">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036509</t>
+          <t xml:space="preserve">200036613</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-06</t>
+          <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8311,17 +8311,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munkegade 18A</t>
+          <t xml:space="preserve">Lille Madsegade 114</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5402005</t>
+          <t xml:space="preserve">5407230</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -8330,16 +8330,16 @@
         </is>
       </c>
       <c r="H139">
-        <v>251</v>
+        <v>734</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036613</t>
+          <t xml:space="preserve">200037141</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-07</t>
+          <t xml:space="preserve">2020-09-15</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8371,17 +8371,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 9</t>
+          <t xml:space="preserve">Sandemandsvej 1A</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5403146</t>
+          <t xml:space="preserve">288308, 288309</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -8390,16 +8390,16 @@
         </is>
       </c>
       <c r="H140">
-        <v>308</v>
+        <v>2282</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">200036610</t>
+          <t xml:space="preserve">200037152</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-07</t>
+          <t xml:space="preserve">2020-09-15</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedeløkken 5</t>
+          <t xml:space="preserve">Sandemandsvej 4B</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146874</t>
+          <t xml:space="preserve">5147263</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -8450,11 +8450,11 @@
         </is>
       </c>
       <c r="H141">
-        <v>2460</v>
+        <v>1243</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037100</t>
+          <t xml:space="preserve">200037111</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandemandsvej 4B</t>
+          <t xml:space="preserve">Smedeløkken 5</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5147263</t>
+          <t xml:space="preserve">5146874</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -8510,11 +8510,11 @@
         </is>
       </c>
       <c r="H142">
-        <v>1243</v>
+        <v>2460</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037111</t>
+          <t xml:space="preserve">200037100</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Madsegade 114</t>
+          <t xml:space="preserve">Fabriksvej 20A</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407230</t>
+          <t xml:space="preserve">5407924</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -8570,16 +8570,16 @@
         </is>
       </c>
       <c r="H143">
-        <v>734</v>
+        <v>612</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037141</t>
+          <t xml:space="preserve">200038276</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-15</t>
+          <t xml:space="preserve">2020-10-01</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabriksvej 20A</t>
+          <t xml:space="preserve">Gudhjemvej 107</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5407924</t>
+          <t xml:space="preserve">5158331</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="H145">
-        <v>612</v>
+        <v>278</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038276</t>
+          <t xml:space="preserve">200038401</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-01</t>
+          <t xml:space="preserve">2020-10-04</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,35 +8731,35 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gudhjemvej 107</t>
+          <t xml:space="preserve">Klintebovej 10</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5158331</t>
+          <t xml:space="preserve">5397680</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H146">
-        <v>278</v>
+        <v>772</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038401</t>
+          <t xml:space="preserve">200038484</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-04</t>
+          <t xml:space="preserve">2020-10-05</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klintebovej 10</t>
+          <t xml:space="preserve">Klintebovej 16</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8806,11 +8806,11 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H147">
-        <v>772</v>
+        <v>347</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -8866,11 +8866,11 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H148">
-        <v>347</v>
+        <v>820</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -8971,35 +8971,35 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klintebovej 16</t>
+          <t xml:space="preserve">Sydskovvej 2</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3740</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397680</t>
+          <t xml:space="preserve">288458, 288459</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H150">
-        <v>820</v>
+        <v>1231</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038484</t>
+          <t xml:space="preserve">200038748</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-05</t>
+          <t xml:space="preserve">2020-10-08</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9091,17 +9091,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndervænget 4</t>
+          <t xml:space="preserve">Byledsgade 86</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5398447</t>
+          <t xml:space="preserve">5410241</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9110,11 +9110,11 @@
         </is>
       </c>
       <c r="H152">
-        <v>310</v>
+        <v>3649</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038941</t>
+          <t xml:space="preserve">200038976</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9151,17 +9151,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byledsgade 86</t>
+          <t xml:space="preserve">Søndervænget 4</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410241</t>
+          <t xml:space="preserve">5398447</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -9170,11 +9170,11 @@
         </is>
       </c>
       <c r="H153">
-        <v>3649</v>
+        <v>310</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038976</t>
+          <t xml:space="preserve">200038941</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9271,17 +9271,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pihls Alle 32</t>
+          <t xml:space="preserve">Dr Kabells Vej 24A</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3782</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5162734</t>
+          <t xml:space="preserve">5409944</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -9290,11 +9290,11 @@
         </is>
       </c>
       <c r="H155">
-        <v>360</v>
+        <v>468</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039090</t>
+          <t xml:space="preserve">200039135</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9331,17 +9331,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr Kabells Vej 24A</t>
+          <t xml:space="preserve">Pihls Alle 32</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3782</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5409944</t>
+          <t xml:space="preserve">5162734</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -9350,11 +9350,11 @@
         </is>
       </c>
       <c r="H156">
-        <v>468</v>
+        <v>360</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039135</t>
+          <t xml:space="preserve">200039090</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9691,17 +9691,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 64</t>
+          <t xml:space="preserve">Møllevænget 1</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3790</t>
+          <t xml:space="preserve">3730</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5400565</t>
+          <t xml:space="preserve">5404249</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -9710,11 +9710,11 @@
         </is>
       </c>
       <c r="H162">
-        <v>605</v>
+        <v>2869</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039746</t>
+          <t xml:space="preserve">200039729</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9751,17 +9751,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevænget 1</t>
+          <t xml:space="preserve">Storegade 64</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3730</t>
+          <t xml:space="preserve">3790</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5404249</t>
+          <t xml:space="preserve">5400565</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -9770,11 +9770,11 @@
         </is>
       </c>
       <c r="H163">
-        <v>2869</v>
+        <v>605</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039729</t>
+          <t xml:space="preserve">200039746</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9811,17 +9811,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 40</t>
+          <t xml:space="preserve">Almindingensvej 23</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3751</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397138</t>
+          <t xml:space="preserve">8348162</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -9830,11 +9830,11 @@
         </is>
       </c>
       <c r="H164">
-        <v>1368</v>
+        <v>423</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039896</t>
+          <t xml:space="preserve">200039893</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paradisvej 6</t>
+          <t xml:space="preserve">Curdtslund 2</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411634</t>
+          <t xml:space="preserve">5411643</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -9890,11 +9890,11 @@
         </is>
       </c>
       <c r="H165">
-        <v>337</v>
+        <v>4582</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039822</t>
+          <t xml:space="preserve">200039847</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9991,17 +9991,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Curdtslund 2</t>
+          <t xml:space="preserve">Nygade 40</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5411643</t>
+          <t xml:space="preserve">5397138</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10010,11 +10010,11 @@
         </is>
       </c>
       <c r="H167">
-        <v>4582</v>
+        <v>1368</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039847</t>
+          <t xml:space="preserve">200039896</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store Torv 6A</t>
+          <t xml:space="preserve">Paradisvej 6</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">7370629</t>
+          <t xml:space="preserve">5411634</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10070,11 +10070,11 @@
         </is>
       </c>
       <c r="H168">
-        <v>1857</v>
+        <v>337</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039835</t>
+          <t xml:space="preserve">200039822</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10171,17 +10171,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Almindingensvej 23</t>
+          <t xml:space="preserve">Store Torv 6A</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">3751</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348162</t>
+          <t xml:space="preserve">7370629</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -10190,11 +10190,11 @@
         </is>
       </c>
       <c r="H170">
-        <v>423</v>
+        <v>1857</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039893</t>
+          <t xml:space="preserve">200039835</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10231,30 +10231,30 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 4</t>
+          <t xml:space="preserve">Kildesgårdsvej 19</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3782</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5162695</t>
+          <t xml:space="preserve">5164440</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H171">
-        <v>1555</v>
+        <v>2054</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040823</t>
+          <t xml:space="preserve">200040831</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10306,11 +10306,11 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H172">
-        <v>2054</v>
+        <v>367</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -10351,30 +10351,30 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildesgårdsvej 19</t>
+          <t xml:space="preserve">Otto Bruuns Plads 1</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5164440</t>
+          <t xml:space="preserve">8348282</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H173">
-        <v>367</v>
+        <v>822</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040831</t>
+          <t xml:space="preserve">200040832</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10411,30 +10411,30 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftelunden 5</t>
+          <t xml:space="preserve">Stadionvej 4</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">3790</t>
+          <t xml:space="preserve">3782</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5401681</t>
+          <t xml:space="preserve">5162695</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H174">
-        <v>4130</v>
+        <v>1555</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040820</t>
+          <t xml:space="preserve">200040823</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10531,17 +10531,17 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otto Bruuns Plads 1</t>
+          <t xml:space="preserve">Toftelunden 1A</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3790</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348282</t>
+          <t xml:space="preserve">8359771</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10550,11 +10550,11 @@
         </is>
       </c>
       <c r="H176">
-        <v>822</v>
+        <v>1439</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040832</t>
+          <t xml:space="preserve">200040821</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftelunden 1A</t>
+          <t xml:space="preserve">Toftelunden 5</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8359771</t>
+          <t xml:space="preserve">5401681</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -10610,11 +10610,11 @@
         </is>
       </c>
       <c r="H177">
-        <v>1439</v>
+        <v>4130</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040821</t>
+          <t xml:space="preserve">200040820</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10651,17 +10651,17 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovløkken 4</t>
+          <t xml:space="preserve">Kirkegade 4</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3770</t>
+          <t xml:space="preserve">3790</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5164475</t>
+          <t xml:space="preserve">8359765</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -10670,11 +10670,11 @@
         </is>
       </c>
       <c r="H178">
-        <v>2346</v>
+        <v>2569</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040869</t>
+          <t xml:space="preserve">200040860</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10711,30 +10711,30 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rø Skolevej 8</t>
+          <t xml:space="preserve">Kirkegade 4</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3790</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">7118089</t>
+          <t xml:space="preserve">8359765</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H179">
-        <v>1265</v>
+        <v>735</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040899</t>
+          <t xml:space="preserve">200040860</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10831,17 +10831,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 4</t>
+          <t xml:space="preserve">Rø Skolevej 8</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">3790</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">8359765</t>
+          <t xml:space="preserve">7118089</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10850,11 +10850,11 @@
         </is>
       </c>
       <c r="H181">
-        <v>2569</v>
+        <v>1265</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040860</t>
+          <t xml:space="preserve">200040899</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10891,30 +10891,30 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 4</t>
+          <t xml:space="preserve">Skovløkken 4</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">3790</t>
+          <t xml:space="preserve">3770</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">8359765</t>
+          <t xml:space="preserve">5164475</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H182">
-        <v>735</v>
+        <v>2346</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040860</t>
+          <t xml:space="preserve">200040869</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnevej 106</t>
+          <t xml:space="preserve">Eskildsgade 15</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5149826</t>
+          <t xml:space="preserve">5396503</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -11150,11 +11150,11 @@
         </is>
       </c>
       <c r="H186">
-        <v>1532</v>
+        <v>820</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051851</t>
+          <t xml:space="preserve">200051846</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11191,17 +11191,17 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestermarievej 16</t>
+          <t xml:space="preserve">Grønningen 30</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700</t>
+          <t xml:space="preserve">3720</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5150673</t>
+          <t xml:space="preserve">8263845</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -11210,11 +11210,11 @@
         </is>
       </c>
       <c r="H187">
-        <v>2393</v>
+        <v>3794</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051848</t>
+          <t xml:space="preserve">200051850</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskildsgade 15</t>
+          <t xml:space="preserve">Klintebovej 16</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11261,20 +11261,20 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5396503</t>
+          <t xml:space="preserve">5397680</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H188">
-        <v>820</v>
+        <v>769</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051846</t>
+          <t xml:space="preserve">200051845</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klintebovej 16</t>
+          <t xml:space="preserve">Rønnevej 106</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11321,20 +11321,20 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5397680</t>
+          <t xml:space="preserve">5149826</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H189">
-        <v>769</v>
+        <v>1532</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051845</t>
+          <t xml:space="preserve">200051851</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11371,17 +11371,17 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 30</t>
+          <t xml:space="preserve">Solstien 1</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">3760</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">8263845</t>
+          <t xml:space="preserve">8348046</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -11390,11 +11390,11 @@
         </is>
       </c>
       <c r="H190">
-        <v>3794</v>
+        <v>1915</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051850</t>
+          <t xml:space="preserve">200051849</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11431,17 +11431,17 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solstien 1</t>
+          <t xml:space="preserve">Vestermarievej 16</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">3760</t>
+          <t xml:space="preserve">3700</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">8348046</t>
+          <t xml:space="preserve">5150673</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -11450,11 +11450,11 @@
         </is>
       </c>
       <c r="H191">
-        <v>1915</v>
+        <v>2393</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051849</t>
+          <t xml:space="preserve">200051848</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnevej 5</t>
+          <t xml:space="preserve">Rønnevej 3</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12581,16 +12581,16 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5399685</t>
+          <t xml:space="preserve">725184, 5399685</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H210">
-        <v>256</v>
+        <v>418</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -12646,11 +12646,11 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H211">
-        <v>418</v>
+        <v>691</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -12706,15 +12706,15 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H212">
-        <v>691</v>
+        <v>618</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878991</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -12766,15 +12766,15 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="H213">
-        <v>618</v>
+        <v>694</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878988</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12826,15 +12826,15 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H214">
-        <v>694</v>
+        <v>795</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878988</t>
+          <t xml:space="preserve">311878984</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -12886,11 +12886,11 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H215">
-        <v>795</v>
+        <v>366</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnevej 3</t>
+          <t xml:space="preserve">Rønnevej 5</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12941,16 +12941,16 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">725184, 5399685</t>
+          <t xml:space="preserve">5399685</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H216">
-        <v>366</v>
+        <v>256</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>

--- a/public/exports/26696348.xlsx
+++ b/public/exports/26696348.xlsx
@@ -12594,7 +12594,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">

--- a/public/exports/26696348.xlsx
+++ b/public/exports/26696348.xlsx
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035071</t>
+          <t xml:space="preserve">200035073</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035229</t>
+          <t xml:space="preserve">200035250</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038976</t>
+          <t xml:space="preserve">200038977</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878991</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878988</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">

--- a/public/exports/26696348.xlsx
+++ b/public/exports/26696348.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L220"/>
+  <dimension ref="A1:M220"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2944,10 +3184,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3004,10 +3249,15 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3064,10 +3314,15 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3124,10 +3379,15 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3184,10 +3444,15 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3244,10 +3509,15 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3304,10 +3574,15 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3364,10 +3639,15 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3424,10 +3704,15 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3484,10 +3769,15 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3544,10 +3834,15 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3604,10 +3899,15 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3664,10 +3964,15 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3724,10 +4029,15 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3784,10 +4094,15 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3844,10 +4159,15 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3904,10 +4224,15 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3964,10 +4289,15 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4024,10 +4354,15 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4084,10 +4419,15 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4144,10 +4484,15 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4204,10 +4549,15 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4264,10 +4614,15 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4324,10 +4679,15 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4384,10 +4744,15 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4444,10 +4809,15 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4504,10 +4874,15 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4564,10 +4939,15 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4624,10 +5004,15 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4684,10 +5069,15 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4744,10 +5134,15 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4804,10 +5199,15 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4864,10 +5264,15 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4924,10 +5329,15 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4984,10 +5394,15 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5044,10 +5459,15 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5104,10 +5524,15 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5164,10 +5589,15 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5224,10 +5654,15 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5284,10 +5719,15 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5344,10 +5784,15 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5404,10 +5849,15 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5464,10 +5914,15 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5524,10 +5979,15 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5584,10 +6044,15 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5644,10 +6109,15 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5704,10 +6174,15 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5764,10 +6239,15 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5824,10 +6304,15 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5884,10 +6369,15 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5944,10 +6434,15 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6004,10 +6499,15 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6064,10 +6564,15 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6124,10 +6629,15 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6184,10 +6694,15 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6244,10 +6759,15 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6304,10 +6824,15 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6364,10 +6889,15 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6424,10 +6954,15 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6484,10 +7019,15 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning I/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-02-25</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning I/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-02-25</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-05-06</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-05-06</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6774,20 +7334,25 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033111</t>
+          <t xml:space="preserve">200033151</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-28</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-28</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-29</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-29</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-29</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7074,20 +7659,25 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033685</t>
+          <t xml:space="preserve">200033687</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-07</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-07</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-08</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-08-05</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-08-10</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-08-11</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-08-13</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7554,20 +8179,25 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035250</t>
+          <t xml:space="preserve">200035229</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-08-13</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-08-23</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-08-26</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-08-27</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-08-30</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-01</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-02</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-02</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-02</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-03</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-06</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-07</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-15</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-15</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-15</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-15</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="L142" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-01</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-01</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-04</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-05</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-05</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-05</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-05</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="L149" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-08</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-11</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9114,20 +9869,25 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038977</t>
+          <t xml:space="preserve">200038976</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-12</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-12</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-13</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-14</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-14</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-14</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-19</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-19</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-24</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-25</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-26</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-26</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="L165" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="L168" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-27</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="L170" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-10</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-11</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-11</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-11</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-11</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="L181" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-11</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="L182" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-31</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="L183" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-05</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-29</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="L185" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS - Botjek Rønne Øst</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
+      <c r="L186" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS - Botjek Rønne Øst</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
+      <c r="L187" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS - Botjek Rønne Øst</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
+      <c r="L188" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS - Botjek Rønne Øst</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
+      <c r="L189" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS - Botjek Rønne Øst</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
+      <c r="L190" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornholms Byggerådgivning ApS - Botjek Rønne Øst</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-11</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
+      <c r="L191" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-07-03</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
+      <c r="L192" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek a/s, Rønne Øst</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-10-07</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
+      <c r="L193" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørfirma Mogens Ørum</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-01-23</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
+      <c r="L194" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørfirma Mogens Ørum</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-01-27</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
+      <c r="L195" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek, Rønne Øst</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-04-10</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
+      <c r="L196" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">KEEN MILJØ- &amp; ENERGIRÅDGIVNING ApS</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
+      <c r="L197" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">KEEN MILJØ- &amp; ENERGIRÅDGIVNING ApS</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
+      <c r="L198" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">KEEN MILJØ- &amp; ENERGIRÅDGIVNING ApS</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
+      <c r="L199" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørfirma Mogens Ørum</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-03-19</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
+      <c r="L200" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørfirma Mogens Ørum</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-13</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="L201" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">Arkitektfirmaet Byg &amp; Bo ApS</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-02</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="L202" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bodal Energi- &amp; Miljørådgivning</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
+      <c r="L203" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-13</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="L204" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-27</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="L205" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
+      <c r="L206" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
+      <c r="L207" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="L208" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="L209" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="L210" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="L211" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="L212" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="L213" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="L215" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
+      <c r="L216" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-24</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
+      <c r="L217" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-15</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
+      <c r="L218" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-15</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="L219" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,21 +14294,26 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-15</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
+      <c r="L220" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L220"/>
+  <autoFilter ref="A1:M220"/>
 </worksheet>
 </file>
--- a/public/exports/26696348.xlsx
+++ b/public/exports/26696348.xlsx
@@ -7334,7 +7334,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033151</t>
+          <t xml:space="preserve">200033111</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033687</t>
+          <t xml:space="preserve">200033685</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035073</t>
+          <t xml:space="preserve">200035071</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
